--- a/sample-data/goc-ho-coffee/04_mua_hang_va_chi_phi_3_thang.xlsx
+++ b/sample-data/goc-ho-coffee/04_mua_hang_va_chi_phi_3_thang.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tóm tắt" sheetId="1" r:id="Ra1e2c238a8944f97"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mua hàng chi phí" sheetId="2" r:id="R70e43fb1927143e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nhà cung cấp" sheetId="3" r:id="R45af9e478661468f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tóm tắt" sheetId="1" r:id="R7794ca61f1004ad3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mua hàng chi phí" sheetId="2" r:id="Rc3ece8d171994d46"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nhà cung cấp" sheetId="3" r:id="R4aeb2ec745734dca"/>
   </x:sheets>
 </x:workbook>
 </file>
